--- a/hazine nakit/nakit.xlsx
+++ b/hazine nakit/nakit.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,79 +421,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>yil</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ay</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>gelir</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gider</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>faiz_disi_gider</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>faiz_odemesi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>faiz_disi_denge</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ozellestirme</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>nakit_denge</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>finansman</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>borclanma_net</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ic_borclanma_net</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>dis_borclanma_net</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -547,7 +535,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -589,7 +577,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -673,7 +661,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -715,7 +703,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -757,7 +745,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -799,7 +787,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -841,7 +829,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -883,7 +871,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -925,7 +913,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -967,7 +955,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -1009,7 +997,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -1051,7 +1039,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -1093,7 +1081,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -1135,7 +1123,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -1177,7 +1165,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -1219,7 +1207,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -1261,7 +1249,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -1303,7 +1291,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -1345,7 +1333,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -1387,7 +1375,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -1429,7 +1417,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -1471,7 +1459,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -1513,7 +1501,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -1555,7 +1543,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -1597,7 +1585,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -1639,7 +1627,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -1681,7 +1669,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -1723,7 +1711,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -1765,7 +1753,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -1807,7 +1795,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -1849,7 +1837,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -1891,7 +1879,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -1933,7 +1921,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -1975,7 +1963,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -2017,7 +2005,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -2061,7 +2049,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -2105,7 +2093,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -2149,7 +2137,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -2193,7 +2181,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -2237,7 +2225,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -2281,7 +2269,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -2325,7 +2313,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -2369,7 +2357,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -2413,7 +2401,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -2457,7 +2445,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -2501,7 +2489,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -2545,7 +2533,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -2589,7 +2577,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -2633,7 +2621,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -2677,7 +2665,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -2721,7 +2709,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -2765,7 +2753,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -2809,7 +2797,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -2853,7 +2841,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -2897,7 +2885,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -2941,7 +2929,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -2985,7 +2973,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -3029,7 +3017,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -3073,7 +3061,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -3117,7 +3105,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -3161,7 +3149,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -3205,7 +3193,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -3249,7 +3237,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -3293,7 +3281,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -3337,7 +3325,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -3381,7 +3369,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -3425,7 +3413,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -3469,7 +3457,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -3513,7 +3501,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -3557,7 +3545,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -3601,7 +3589,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -3645,7 +3633,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -3689,7 +3677,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -3733,7 +3721,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -3777,7 +3765,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -3821,7 +3809,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -3865,7 +3853,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -3909,7 +3897,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -3953,7 +3941,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -3997,7 +3985,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -4041,7 +4029,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -4085,7 +4073,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -4129,7 +4117,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -4173,7 +4161,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -4217,7 +4205,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -4261,7 +4249,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -4305,7 +4293,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -4349,7 +4337,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -4393,7 +4381,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -4437,7 +4425,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -4481,7 +4469,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -4525,7 +4513,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -4569,7 +4557,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -4613,7 +4601,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -4657,7 +4645,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -4701,7 +4689,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -4745,7 +4733,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -4789,7 +4777,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -4833,7 +4821,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -4877,7 +4865,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -4921,7 +4909,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -4965,7 +4953,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -5009,7 +4997,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -5053,7 +5041,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -5097,7 +5085,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -5141,7 +5129,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -5185,7 +5173,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -5229,7 +5217,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -5273,7 +5261,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -5317,7 +5305,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -5361,7 +5349,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -5405,7 +5393,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -5449,7 +5437,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -5493,7 +5481,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -5537,7 +5525,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -5581,7 +5569,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -5625,7 +5613,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -5669,7 +5657,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -5713,7 +5701,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -5757,7 +5745,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -5801,7 +5789,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -5845,7 +5833,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -5889,7 +5877,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -5933,7 +5921,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -5977,7 +5965,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -6021,7 +6009,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -6065,7 +6053,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -6109,7 +6097,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -6153,7 +6141,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -6197,7 +6185,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -6241,7 +6229,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -6285,7 +6273,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -6329,7 +6317,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -6373,7 +6361,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -6417,7 +6405,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -6461,7 +6449,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -6505,7 +6493,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -6549,7 +6537,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -6593,7 +6581,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -6637,7 +6625,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -6681,7 +6669,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -6725,7 +6713,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -6769,7 +6757,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -6813,7 +6801,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -6857,7 +6845,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -6901,7 +6889,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -6945,7 +6933,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -6989,7 +6977,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -7033,7 +7021,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -7077,7 +7065,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -7121,7 +7109,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -7165,7 +7153,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -7209,7 +7197,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -7253,7 +7241,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -7297,7 +7285,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -7341,7 +7329,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -7385,7 +7373,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -7429,7 +7417,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -7473,7 +7461,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -7517,7 +7505,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -7561,7 +7549,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -7605,7 +7593,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -7649,7 +7637,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -7693,7 +7681,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -7737,7 +7725,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -7781,7 +7769,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -7825,7 +7813,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -7869,7 +7857,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -7913,7 +7901,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -7957,7 +7945,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -8001,7 +7989,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -8045,7 +8033,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -8089,7 +8077,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -8133,7 +8121,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -8177,7 +8165,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -8221,7 +8209,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -8265,7 +8253,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -8309,7 +8297,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -8353,7 +8341,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -8397,7 +8385,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -8441,7 +8429,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -8485,7 +8473,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -8529,7 +8517,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -8573,7 +8561,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -8617,7 +8605,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -8661,7 +8649,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -8705,7 +8693,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -8749,7 +8737,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -8793,7 +8781,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -8837,7 +8825,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -8881,7 +8869,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -8925,7 +8913,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -8969,7 +8957,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -9013,7 +9001,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -9057,7 +9045,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -9101,7 +9089,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -9145,7 +9133,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -9189,7 +9177,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -9233,7 +9221,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -9277,7 +9265,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -9321,7 +9309,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -9365,7 +9353,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -9409,7 +9397,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B206" t="n">
@@ -9453,7 +9441,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B207" t="n">
@@ -9497,7 +9485,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B208" t="n">
@@ -9541,7 +9529,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B209" t="n">
@@ -9585,7 +9573,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B210" t="n">
@@ -9629,7 +9617,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B211" t="n">
@@ -9673,7 +9661,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B212" t="n">
@@ -9717,7 +9705,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B213" t="n">
@@ -9761,7 +9749,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B214" t="n">
@@ -9805,7 +9793,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B215" t="n">
@@ -9849,7 +9837,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B216" t="n">
@@ -9893,7 +9881,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B217" t="n">
@@ -9937,7 +9925,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B218" t="n">
@@ -9981,7 +9969,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B219" t="n">
@@ -10025,7 +10013,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B220" t="n">
@@ -10069,7 +10057,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B221" t="n">
@@ -10113,7 +10101,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B222" t="n">
@@ -10157,7 +10145,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B223" t="n">
@@ -10201,7 +10189,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B224" t="n">
@@ -10245,7 +10233,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B225" t="n">
@@ -10289,7 +10277,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B226" t="n">
@@ -10333,7 +10321,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B227" t="n">
@@ -10377,7 +10365,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B228" t="n">
@@ -10421,7 +10409,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B229" t="n">
@@ -10465,7 +10453,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B230" t="n">
@@ -10509,7 +10497,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B231" t="n">
@@ -10553,7 +10541,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B232" t="n">
@@ -10597,7 +10585,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B233" t="n">
@@ -10641,7 +10629,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B234" t="n">

--- a/hazine nakit/nakit.xlsx
+++ b/hazine nakit/nakit.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,79 +433,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>yil</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ay</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>gelir</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>gider</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>faiz_disi_gider</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>faiz_odemesi</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>faiz_disi_denge</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ozellestirme</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>nakit_denge</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>finansman</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>borclanma_net</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ic_borclanma_net</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dis_borclanma_net</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -535,7 +547,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -577,7 +589,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -661,7 +673,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -703,7 +715,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -745,7 +757,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -787,7 +799,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -829,7 +841,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -871,7 +883,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -913,7 +925,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -955,7 +967,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -997,7 +1009,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -1039,7 +1051,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -1081,7 +1093,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -1123,7 +1135,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -1165,7 +1177,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -1207,7 +1219,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -1249,7 +1261,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -1291,7 +1303,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -1333,7 +1345,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -1375,7 +1387,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -1417,7 +1429,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -1459,7 +1471,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -1501,7 +1513,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -1543,7 +1555,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -1585,7 +1597,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -1627,7 +1639,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -1669,7 +1681,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -1711,7 +1723,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -1753,7 +1765,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -1795,7 +1807,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -1837,7 +1849,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -1879,7 +1891,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -1921,7 +1933,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -1963,7 +1975,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -2005,7 +2017,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -2093,7 +2105,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -2137,7 +2149,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -2181,7 +2193,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -2225,7 +2237,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -2269,7 +2281,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -2313,7 +2325,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -2357,7 +2369,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -2401,7 +2413,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -2445,7 +2457,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -2489,7 +2501,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -2533,7 +2545,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -2577,7 +2589,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -2621,7 +2633,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -2665,7 +2677,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -2709,7 +2721,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -2753,7 +2765,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -2797,7 +2809,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -2841,7 +2853,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -2885,7 +2897,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -2929,7 +2941,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -2973,7 +2985,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -3017,7 +3029,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -3061,7 +3073,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -3105,7 +3117,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -3149,7 +3161,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -3193,7 +3205,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -3237,7 +3249,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -3281,7 +3293,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -3325,7 +3337,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -3369,7 +3381,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -3413,7 +3425,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -3457,7 +3469,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -3501,7 +3513,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -3545,7 +3557,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -3589,7 +3601,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -3633,7 +3645,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -3677,7 +3689,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -3721,7 +3733,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -3765,7 +3777,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -3809,7 +3821,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -3853,7 +3865,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -3897,7 +3909,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -3941,7 +3953,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -3985,7 +3997,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -4029,7 +4041,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -4073,7 +4085,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -4117,7 +4129,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -4161,7 +4173,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -4205,7 +4217,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -4249,7 +4261,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -4293,7 +4305,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -4337,7 +4349,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -4381,7 +4393,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -4425,7 +4437,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -4469,7 +4481,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -4513,7 +4525,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -4557,7 +4569,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -4601,7 +4613,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -4645,7 +4657,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -4689,7 +4701,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -4733,7 +4745,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -4777,7 +4789,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -4821,7 +4833,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -4865,7 +4877,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -4909,7 +4921,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -4953,7 +4965,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -4997,7 +5009,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -5041,7 +5053,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -5085,7 +5097,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -5129,7 +5141,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -5173,7 +5185,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -5217,7 +5229,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -5261,7 +5273,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -5305,7 +5317,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -5349,7 +5361,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -5393,7 +5405,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -5437,7 +5449,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -5481,7 +5493,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -5525,7 +5537,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -5569,7 +5581,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -5613,7 +5625,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -5657,7 +5669,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -5701,7 +5713,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -5745,7 +5757,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -5789,7 +5801,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -5833,7 +5845,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -5877,7 +5889,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -5921,7 +5933,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -5965,7 +5977,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -6009,7 +6021,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -6053,7 +6065,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -6097,7 +6109,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -6141,7 +6153,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -6185,7 +6197,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -6229,7 +6241,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -6273,7 +6285,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -6317,7 +6329,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -6361,7 +6373,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -6405,7 +6417,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -6449,7 +6461,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -6493,7 +6505,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -6537,7 +6549,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -6581,7 +6593,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -6625,7 +6637,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -6669,7 +6681,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -6713,7 +6725,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -6757,7 +6769,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -6801,7 +6813,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -6845,7 +6857,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -6889,7 +6901,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -6933,7 +6945,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -6977,7 +6989,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -7021,7 +7033,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -7065,7 +7077,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -7109,7 +7121,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -7153,7 +7165,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -7197,7 +7209,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -7241,7 +7253,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -7285,7 +7297,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -7329,7 +7341,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -7373,7 +7385,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -7417,7 +7429,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -7461,7 +7473,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -7505,7 +7517,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -7549,7 +7561,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -7593,7 +7605,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -7637,7 +7649,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -7681,7 +7693,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -7725,7 +7737,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -7769,7 +7781,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -7813,7 +7825,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -7857,7 +7869,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -7901,7 +7913,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -7945,7 +7957,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -7989,7 +8001,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -8033,7 +8045,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -8077,7 +8089,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -8121,7 +8133,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -8165,7 +8177,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -8209,7 +8221,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -8253,7 +8265,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -8297,7 +8309,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -8341,7 +8353,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -8385,7 +8397,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -8429,7 +8441,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -8473,7 +8485,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -8517,7 +8529,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -8561,7 +8573,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -8605,7 +8617,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -8649,7 +8661,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -8693,7 +8705,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -8737,7 +8749,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -8781,7 +8793,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -8825,7 +8837,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -8869,7 +8881,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -8913,7 +8925,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -8957,7 +8969,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -9001,7 +9013,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -9045,7 +9057,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -9089,7 +9101,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -9133,7 +9145,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -9177,7 +9189,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -9221,7 +9233,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -9265,7 +9277,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -9309,7 +9321,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -9353,7 +9365,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -9397,7 +9409,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B206" t="n">
@@ -9441,7 +9453,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B207" t="n">
@@ -9485,7 +9497,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B208" t="n">
@@ -9529,7 +9541,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B209" t="n">
@@ -9573,7 +9585,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B210" t="n">
@@ -9617,7 +9629,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B211" t="n">
@@ -9661,7 +9673,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B212" t="n">
@@ -9705,7 +9717,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B213" t="n">
@@ -9749,7 +9761,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B214" t="n">
@@ -9793,7 +9805,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B215" t="n">
@@ -9837,7 +9849,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B216" t="n">
@@ -9881,7 +9893,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B217" t="n">
@@ -9925,7 +9937,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B218" t="n">
@@ -9969,7 +9981,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B219" t="n">
@@ -10013,7 +10025,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B220" t="n">
@@ -10057,7 +10069,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B221" t="n">
@@ -10101,7 +10113,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B222" t="n">
@@ -10145,7 +10157,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B223" t="n">
@@ -10189,7 +10201,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B224" t="n">
@@ -10233,7 +10245,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B225" t="n">
@@ -10277,7 +10289,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B226" t="n">
@@ -10321,7 +10333,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B227" t="n">
@@ -10365,7 +10377,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B228" t="n">
@@ -10409,7 +10421,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B229" t="n">
@@ -10453,7 +10465,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B230" t="n">
@@ -10497,7 +10509,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B231" t="n">
@@ -10541,7 +10553,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B232" t="n">
@@ -10585,7 +10597,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B233" t="n">
@@ -10629,7 +10641,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B234" t="n">

--- a/hazine nakit/nakit.xlsx
+++ b/hazine nakit/nakit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N234"/>
+  <dimension ref="A1:N235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10639,7 +10639,7 @@
         <v>6</v>
       </c>
       <c r="D234" t="n">
-        <v>1513685</v>
+        <v>1512229.5</v>
       </c>
       <c r="E234" t="n">
         <v>1462926.24</v>
@@ -10651,25 +10651,69 @@
         <v>189440.71</v>
       </c>
       <c r="H234" t="n">
-        <v>240199.47</v>
+        <v>238743.97</v>
       </c>
       <c r="I234" t="n">
-        <v>0</v>
+        <v>798.72</v>
       </c>
       <c r="J234" t="n">
-        <v>50758.76</v>
+        <v>50101.98</v>
       </c>
       <c r="K234" t="n">
-        <v>-50758.76</v>
+        <v>-50101.98</v>
       </c>
       <c r="L234" t="n">
-        <v>-6510.67</v>
+        <v>-9688.26</v>
       </c>
       <c r="M234" t="n">
         <v>116497.05</v>
       </c>
       <c r="N234" t="n">
-        <v>-123007.71</v>
+        <v>-126185.31</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B235" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C235" t="n">
+        <v>7</v>
+      </c>
+      <c r="D235" t="n">
+        <v>1394899.46</v>
+      </c>
+      <c r="E235" t="n">
+        <v>1790549.48</v>
+      </c>
+      <c r="F235" t="n">
+        <v>1464639.54</v>
+      </c>
+      <c r="G235" t="n">
+        <v>325909.94</v>
+      </c>
+      <c r="H235" t="n">
+        <v>-69740.08</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>-395650.02</v>
+      </c>
+      <c r="K235" t="n">
+        <v>395650.02</v>
+      </c>
+      <c r="L235" t="n">
+        <v>315730.84</v>
+      </c>
+      <c r="M235" t="n">
+        <v>199245.02</v>
+      </c>
+      <c r="N235" t="n">
+        <v>116485.82</v>
       </c>
     </row>
   </sheetData>

--- a/hazine nakit/nakit.xlsx
+++ b/hazine nakit/nakit.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,79 +433,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>yil</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>ay</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>gelir</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>gider</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>faiz_disi_gider</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>faiz_odemesi</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>faiz_disi_denge</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ozellestirme</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>nakit_denge</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>finansman</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>borclanma_net</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ic_borclanma_net</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dis_borclanma_net</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -535,7 +547,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -577,7 +589,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -619,7 +631,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -661,7 +673,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -703,7 +715,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -745,7 +757,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -787,7 +799,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -829,7 +841,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -871,7 +883,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -913,7 +925,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -955,7 +967,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -997,7 +1009,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -1039,7 +1051,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -1081,7 +1093,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -1123,7 +1135,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -1165,7 +1177,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -1207,7 +1219,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -1249,7 +1261,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -1291,7 +1303,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -1333,7 +1345,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -1375,7 +1387,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -1417,7 +1429,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -1459,7 +1471,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -1501,7 +1513,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -1543,7 +1555,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -1585,7 +1597,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -1627,7 +1639,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -1669,7 +1681,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -1711,7 +1723,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -1753,7 +1765,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -1795,7 +1807,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -1837,7 +1849,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -1879,7 +1891,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -1921,7 +1933,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -1963,7 +1975,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -2005,7 +2017,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -2049,7 +2061,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -2093,7 +2105,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -2137,7 +2149,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -2181,7 +2193,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -2225,7 +2237,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -2269,7 +2281,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -2313,7 +2325,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -2357,7 +2369,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -2401,7 +2413,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -2445,7 +2457,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -2489,7 +2501,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -2533,7 +2545,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -2577,7 +2589,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -2621,7 +2633,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -2665,7 +2677,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -2709,7 +2721,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -2753,7 +2765,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -2797,7 +2809,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -2841,7 +2853,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -2885,7 +2897,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -2929,7 +2941,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -2973,7 +2985,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -3017,7 +3029,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -3061,7 +3073,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -3105,7 +3117,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -3149,7 +3161,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -3193,7 +3205,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -3237,7 +3249,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -3281,7 +3293,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -3325,7 +3337,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -3369,7 +3381,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -3413,7 +3425,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -3457,7 +3469,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -3501,7 +3513,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -3545,7 +3557,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -3589,7 +3601,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -3633,7 +3645,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -3677,7 +3689,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -3721,7 +3733,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -3765,7 +3777,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -3809,7 +3821,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -3853,7 +3865,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -3897,7 +3909,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -3941,7 +3953,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -3985,7 +3997,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -4029,7 +4041,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -4073,7 +4085,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -4117,7 +4129,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -4161,7 +4173,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -4205,7 +4217,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -4249,7 +4261,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -4293,7 +4305,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -4337,7 +4349,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -4381,7 +4393,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -4425,7 +4437,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -4469,7 +4481,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -4513,7 +4525,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -4557,7 +4569,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -4601,7 +4613,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -4645,7 +4657,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -4689,7 +4701,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -4733,7 +4745,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -4777,7 +4789,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -4821,7 +4833,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -4865,7 +4877,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -4909,7 +4921,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -4953,7 +4965,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -4997,7 +5009,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -5041,7 +5053,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -5085,7 +5097,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -5129,7 +5141,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -5173,7 +5185,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -5217,7 +5229,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -5261,7 +5273,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -5305,7 +5317,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -5349,7 +5361,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -5393,7 +5405,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -5437,7 +5449,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -5481,7 +5493,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -5525,7 +5537,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -5569,7 +5581,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -5613,7 +5625,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -5657,7 +5669,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -5701,7 +5713,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -5745,7 +5757,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -5789,7 +5801,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -5833,7 +5845,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -5877,7 +5889,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -5921,7 +5933,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -5965,7 +5977,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -6009,7 +6021,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -6053,7 +6065,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -6097,7 +6109,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -6141,7 +6153,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -6185,7 +6197,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -6229,7 +6241,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -6273,7 +6285,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -6317,7 +6329,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -6361,7 +6373,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -6405,7 +6417,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -6449,7 +6461,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -6493,7 +6505,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -6537,7 +6549,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -6581,7 +6593,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -6625,7 +6637,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -6669,7 +6681,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -6713,7 +6725,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -6757,7 +6769,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -6801,7 +6813,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -6845,7 +6857,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -6889,7 +6901,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -6933,7 +6945,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -6977,7 +6989,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -7021,7 +7033,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -7065,7 +7077,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -7109,7 +7121,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -7153,7 +7165,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -7197,7 +7209,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -7241,7 +7253,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -7285,7 +7297,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -7329,7 +7341,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -7373,7 +7385,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -7417,7 +7429,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -7461,7 +7473,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -7505,7 +7517,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -7549,7 +7561,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -7593,7 +7605,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -7637,7 +7649,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -7681,7 +7693,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -7725,7 +7737,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -7769,7 +7781,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -7813,7 +7825,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -7857,7 +7869,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -7901,7 +7913,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -7945,7 +7957,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -7989,7 +8001,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -8033,7 +8045,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -8077,7 +8089,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -8121,7 +8133,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -8165,7 +8177,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -8209,7 +8221,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -8253,7 +8265,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -8297,7 +8309,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -8341,7 +8353,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -8385,7 +8397,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -8429,7 +8441,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -8473,7 +8485,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -8517,7 +8529,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -8561,7 +8573,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -8605,7 +8617,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -8649,7 +8661,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -8693,7 +8705,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -8737,7 +8749,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -8781,7 +8793,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -8825,7 +8837,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -8869,7 +8881,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -8913,7 +8925,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -8957,7 +8969,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -9001,7 +9013,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -9045,7 +9057,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -9089,7 +9101,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -9133,7 +9145,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -9177,7 +9189,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -9221,7 +9233,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -9265,7 +9277,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -9309,7 +9321,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -9353,7 +9365,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -9397,7 +9409,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B206" t="n">
@@ -9441,7 +9453,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B207" t="n">
@@ -9485,7 +9497,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B208" t="n">
@@ -9529,7 +9541,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B209" t="n">
@@ -9573,7 +9585,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B210" t="n">
@@ -9617,7 +9629,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B211" t="n">
@@ -9661,7 +9673,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B212" t="n">
@@ -9705,7 +9717,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B213" t="n">
@@ -9749,7 +9761,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B214" t="n">
@@ -9793,7 +9805,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B215" t="n">
@@ -9837,7 +9849,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B216" t="n">
@@ -9881,7 +9893,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B217" t="n">
@@ -9925,7 +9937,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B218" t="n">
@@ -9969,7 +9981,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B219" t="n">
@@ -10013,7 +10025,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B220" t="n">
@@ -10057,7 +10069,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B221" t="n">
@@ -10101,7 +10113,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B222" t="n">
@@ -10145,7 +10157,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B223" t="n">
@@ -10189,7 +10201,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B224" t="n">
@@ -10233,7 +10245,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B225" t="n">
@@ -10277,7 +10289,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B226" t="n">
@@ -10321,7 +10333,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B227" t="n">
@@ -10365,7 +10377,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B228" t="n">
@@ -10409,7 +10421,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B229" t="n">
@@ -10453,7 +10465,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B230" t="n">
@@ -10497,7 +10509,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B231" t="n">
@@ -10541,7 +10553,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B232" t="n">
@@ -10585,7 +10597,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B233" t="n">
@@ -10629,7 +10641,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B234" t="n">
@@ -10673,7 +10685,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>46204</v>
       </c>
       <c r="B235" t="n">

--- a/hazine nakit/nakit.xlsx
+++ b/hazine nakit/nakit.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aylik" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,79 +421,79 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tarih</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>yil</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ay</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>gelir</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>gider</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>faiz_disi_gider</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>faiz_odemesi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>faiz_disi_denge</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ozellestirme</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>nakit_denge</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>finansman</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>borclanma_net</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ic_borclanma_net</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>dis_borclanma_net</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -547,7 +535,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -589,7 +577,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -631,7 +619,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -673,7 +661,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -715,7 +703,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -757,7 +745,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -799,7 +787,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -841,7 +829,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -883,7 +871,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -925,7 +913,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -967,7 +955,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -1009,7 +997,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -1051,7 +1039,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -1093,7 +1081,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -1135,7 +1123,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
@@ -1177,7 +1165,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -1219,7 +1207,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -1261,7 +1249,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -1303,7 +1291,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -1345,7 +1333,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -1387,7 +1375,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -1429,7 +1417,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -1471,7 +1459,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -1513,7 +1501,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -1555,7 +1543,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -1597,7 +1585,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -1639,7 +1627,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -1681,7 +1669,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -1723,7 +1711,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -1765,7 +1753,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -1807,7 +1795,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -1849,7 +1837,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -1891,7 +1879,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -1933,7 +1921,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -1975,7 +1963,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -2017,7 +2005,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -2061,7 +2049,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -2105,7 +2093,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -2149,7 +2137,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -2193,7 +2181,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -2237,7 +2225,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -2281,7 +2269,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -2325,7 +2313,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -2369,7 +2357,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -2413,7 +2401,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -2457,7 +2445,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -2501,7 +2489,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -2545,7 +2533,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -2589,7 +2577,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -2633,7 +2621,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
@@ -2677,7 +2665,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -2721,7 +2709,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -2765,7 +2753,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
@@ -2809,7 +2797,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -2853,7 +2841,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -2897,7 +2885,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -2941,7 +2929,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -2985,7 +2973,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -3029,7 +3017,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -3073,7 +3061,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -3117,7 +3105,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -3161,7 +3149,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -3205,7 +3193,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -3249,7 +3237,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -3293,7 +3281,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -3337,7 +3325,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -3381,7 +3369,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -3425,7 +3413,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -3469,7 +3457,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -3513,7 +3501,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -3557,7 +3545,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -3601,7 +3589,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -3645,7 +3633,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -3689,7 +3677,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -3733,7 +3721,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -3777,7 +3765,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -3821,7 +3809,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -3865,7 +3853,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -3909,7 +3897,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -3953,7 +3941,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -3997,7 +3985,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
@@ -4041,7 +4029,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -4085,7 +4073,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -4129,7 +4117,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -4173,7 +4161,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -4217,7 +4205,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -4261,7 +4249,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
@@ -4305,7 +4293,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -4349,7 +4337,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -4393,7 +4381,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -4437,7 +4425,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
@@ -4481,7 +4469,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -4525,7 +4513,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -4569,7 +4557,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -4613,7 +4601,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -4657,7 +4645,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -4701,7 +4689,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -4745,7 +4733,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -4789,7 +4777,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -4833,7 +4821,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -4877,7 +4865,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
@@ -4921,7 +4909,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -4965,7 +4953,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -5009,7 +4997,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -5053,7 +5041,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -5097,7 +5085,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -5141,7 +5129,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -5185,7 +5173,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -5229,7 +5217,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -5273,7 +5261,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -5317,7 +5305,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -5361,7 +5349,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -5405,7 +5393,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -5449,7 +5437,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -5493,7 +5481,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -5537,7 +5525,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -5581,7 +5569,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -5625,7 +5613,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -5669,7 +5657,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -5713,7 +5701,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>42005</v>
       </c>
       <c r="B122" t="n">
@@ -5757,7 +5745,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>42036</v>
       </c>
       <c r="B123" t="n">
@@ -5801,7 +5789,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>42064</v>
       </c>
       <c r="B124" t="n">
@@ -5845,7 +5833,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>42095</v>
       </c>
       <c r="B125" t="n">
@@ -5889,7 +5877,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>42125</v>
       </c>
       <c r="B126" t="n">
@@ -5933,7 +5921,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>42156</v>
       </c>
       <c r="B127" t="n">
@@ -5977,7 +5965,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>42186</v>
       </c>
       <c r="B128" t="n">
@@ -6021,7 +6009,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>42217</v>
       </c>
       <c r="B129" t="n">
@@ -6065,7 +6053,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>42248</v>
       </c>
       <c r="B130" t="n">
@@ -6109,7 +6097,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>42278</v>
       </c>
       <c r="B131" t="n">
@@ -6153,7 +6141,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>42309</v>
       </c>
       <c r="B132" t="n">
@@ -6197,7 +6185,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="B133" t="n">
@@ -6241,7 +6229,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="B134" t="n">
@@ -6285,7 +6273,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>42401</v>
       </c>
       <c r="B135" t="n">
@@ -6329,7 +6317,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>42430</v>
       </c>
       <c r="B136" t="n">
@@ -6373,7 +6361,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>42461</v>
       </c>
       <c r="B137" t="n">
@@ -6417,7 +6405,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>42491</v>
       </c>
       <c r="B138" t="n">
@@ -6461,7 +6449,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>42522</v>
       </c>
       <c r="B139" t="n">
@@ -6505,7 +6493,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="B140" t="n">
@@ -6549,7 +6537,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>42583</v>
       </c>
       <c r="B141" t="n">
@@ -6593,7 +6581,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>42614</v>
       </c>
       <c r="B142" t="n">
@@ -6637,7 +6625,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>42644</v>
       </c>
       <c r="B143" t="n">
@@ -6681,7 +6669,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>42675</v>
       </c>
       <c r="B144" t="n">
@@ -6725,7 +6713,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="B145" t="n">
@@ -6769,7 +6757,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>42736</v>
       </c>
       <c r="B146" t="n">
@@ -6813,7 +6801,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>42767</v>
       </c>
       <c r="B147" t="n">
@@ -6857,7 +6845,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>42795</v>
       </c>
       <c r="B148" t="n">
@@ -6901,7 +6889,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>42826</v>
       </c>
       <c r="B149" t="n">
@@ -6945,7 +6933,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>42856</v>
       </c>
       <c r="B150" t="n">
@@ -6989,7 +6977,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>42887</v>
       </c>
       <c r="B151" t="n">
@@ -7033,7 +7021,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>42917</v>
       </c>
       <c r="B152" t="n">
@@ -7077,7 +7065,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>42948</v>
       </c>
       <c r="B153" t="n">
@@ -7121,7 +7109,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>42979</v>
       </c>
       <c r="B154" t="n">
@@ -7165,7 +7153,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43009</v>
       </c>
       <c r="B155" t="n">
@@ -7209,7 +7197,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43040</v>
       </c>
       <c r="B156" t="n">
@@ -7253,7 +7241,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="B157" t="n">
@@ -7297,7 +7285,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43101</v>
       </c>
       <c r="B158" t="n">
@@ -7341,7 +7329,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B159" t="n">
@@ -7385,7 +7373,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B160" t="n">
@@ -7429,7 +7417,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B161" t="n">
@@ -7473,7 +7461,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B162" t="n">
@@ -7517,7 +7505,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B163" t="n">
@@ -7561,7 +7549,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B164" t="n">
@@ -7605,7 +7593,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B165" t="n">
@@ -7649,7 +7637,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B166" t="n">
@@ -7693,7 +7681,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B167" t="n">
@@ -7737,7 +7725,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B168" t="n">
@@ -7781,7 +7769,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B169" t="n">
@@ -7825,7 +7813,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B170" t="n">
@@ -7869,7 +7857,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B171" t="n">
@@ -7913,7 +7901,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B172" t="n">
@@ -7957,7 +7945,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B173" t="n">
@@ -8001,7 +7989,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B174" t="n">
@@ -8045,7 +8033,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B175" t="n">
@@ -8089,7 +8077,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B176" t="n">
@@ -8133,7 +8121,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B177" t="n">
@@ -8177,7 +8165,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B178" t="n">
@@ -8221,7 +8209,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B179" t="n">
@@ -8265,7 +8253,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B180" t="n">
@@ -8309,7 +8297,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B181" t="n">
@@ -8353,7 +8341,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B182" t="n">
@@ -8397,7 +8385,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B183" t="n">
@@ -8441,7 +8429,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B184" t="n">
@@ -8485,7 +8473,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B185" t="n">
@@ -8529,7 +8517,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B186" t="n">
@@ -8573,7 +8561,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B187" t="n">
@@ -8617,7 +8605,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B188" t="n">
@@ -8661,7 +8649,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B189" t="n">
@@ -8705,7 +8693,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B190" t="n">
@@ -8749,7 +8737,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B191" t="n">
@@ -8793,7 +8781,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B192" t="n">
@@ -8837,7 +8825,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B193" t="n">
@@ -8881,7 +8869,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B194" t="n">
@@ -8925,7 +8913,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B195" t="n">
@@ -8969,7 +8957,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B196" t="n">
@@ -9013,7 +9001,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B197" t="n">
@@ -9057,7 +9045,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B198" t="n">
@@ -9101,7 +9089,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B199" t="n">
@@ -9145,7 +9133,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B200" t="n">
@@ -9189,7 +9177,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B201" t="n">
@@ -9233,7 +9221,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B202" t="n">
@@ -9277,7 +9265,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B203" t="n">
@@ -9321,7 +9309,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B204" t="n">
@@ -9365,7 +9353,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B205" t="n">
@@ -9409,7 +9397,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B206" t="n">
@@ -9453,7 +9441,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B207" t="n">
@@ -9497,7 +9485,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B208" t="n">
@@ -9541,7 +9529,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B209" t="n">
@@ -9585,7 +9573,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B210" t="n">
@@ -9629,7 +9617,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B211" t="n">
@@ -9673,7 +9661,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B212" t="n">
@@ -9717,7 +9705,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B213" t="n">
@@ -9761,7 +9749,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B214" t="n">
@@ -9805,7 +9793,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B215" t="n">
@@ -9849,7 +9837,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B216" t="n">
@@ -9893,7 +9881,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B217" t="n">
@@ -9937,7 +9925,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B218" t="n">
@@ -9981,7 +9969,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B219" t="n">
@@ -10025,7 +10013,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B220" t="n">
@@ -10069,7 +10057,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B221" t="n">
@@ -10113,7 +10101,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B222" t="n">
@@ -10157,7 +10145,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B223" t="n">
@@ -10201,7 +10189,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B224" t="n">
@@ -10245,7 +10233,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B225" t="n">
@@ -10289,7 +10277,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B226" t="n">
@@ -10333,7 +10321,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B227" t="n">
@@ -10377,7 +10365,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B228" t="n">
@@ -10421,7 +10409,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B229" t="n">
@@ -10465,7 +10453,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>46054</v>
       </c>
       <c r="B230" t="n">
@@ -10509,7 +10497,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>46082</v>
       </c>
       <c r="B231" t="n">
@@ -10553,7 +10541,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>46113</v>
       </c>
       <c r="B232" t="n">
@@ -10597,7 +10585,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>46143</v>
       </c>
       <c r="B233" t="n">
@@ -10641,7 +10629,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>46174</v>
       </c>
       <c r="B234" t="n">
@@ -10685,7 +10673,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>46204</v>
       </c>
       <c r="B235" t="n">
